--- a/assets/dummy_data.xlsx
+++ b/assets/dummy_data.xlsx
@@ -1,26 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\he184239\Git\ExcelControlCharts\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\he162696\Documents\ExcelControlCharts\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4D02069-0B5D-4F15-BFEB-3172F198F1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B90C4CA-ECCD-4D42-9CCF-FEEEA7954A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13996" xr2:uid="{B4DE27E6-3CDA-4D86-9B4B-E26F47FA9977}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="20640" windowHeight="13200" tabRatio="752" firstSheet="1" activeTab="1" xr2:uid="{B4DE27E6-3CDA-4D86-9B4B-E26F47FA9977}"/>
   </bookViews>
   <sheets>
     <sheet name="dummy_data" sheetId="1" r:id="rId1"/>
+    <sheet name="Run charts" sheetId="14" r:id="rId2"/>
+    <sheet name="I charts" sheetId="2" r:id="rId3"/>
+    <sheet name="MR Charts" sheetId="3" r:id="rId4"/>
+    <sheet name="P Charts" sheetId="4" r:id="rId5"/>
+    <sheet name="P' Chart" sheetId="5" r:id="rId6"/>
+    <sheet name="U Chart" sheetId="6" r:id="rId7"/>
+    <sheet name="U' Chart" sheetId="7" r:id="rId8"/>
+    <sheet name="C Charts" sheetId="8" r:id="rId9"/>
+    <sheet name="Xbar Charts" sheetId="9" r:id="rId10"/>
+    <sheet name="S Charts" sheetId="10" r:id="rId11"/>
+    <sheet name="G Charts" sheetId="11" r:id="rId12"/>
+    <sheet name="T Charts" sheetId="12" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="33">
   <si>
     <t>country</t>
   </si>
@@ -74,6 +99,51 @@
   </si>
   <si>
     <t>J</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Harmed</t>
+  </si>
+  <si>
+    <t>Patients</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Sum of Met Target</t>
+  </si>
+  <si>
+    <t>Sum of Attendances</t>
+  </si>
+  <si>
+    <t>Patient Days</t>
+  </si>
+  <si>
+    <t>Adverse Events</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Date of Fatality</t>
+  </si>
+  <si>
+    <t>Surgeries</t>
   </si>
 </sst>
 </file>
@@ -557,9 +627,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -605,7 +676,46 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="14">
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -622,17 +732,826 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>117475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>117475</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C26B224-B7C6-0DF9-0D69-1854726B5680}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2549525" y="879475"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB8B3661-0BD2-38E3-9D71-B1B8D30CB351}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3444875" y="669925"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F67DDE9C-6FCB-B9CD-49EE-E505BFEBA0B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3092450" y="412750"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0361808B-2B85-2F91-B1E4-F297A4C10EBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2863850" y="555625"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>187325</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>153193</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>79374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F734B5-59F4-5617-E721-9B86624FB317}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2835275" y="1105693"/>
+          <a:ext cx="5489575" cy="4117181"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF345C49-4C2D-E1EF-64FE-E4B7888115EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3883025" y="403225"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4442BB0F-06A4-C180-1B89-A4A9F65600F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3787775" y="946150"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4181234-86D9-87FB-A382-A04F8E8DA628}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3835400" y="479425"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{724BD268-1FCE-2FF8-3295-527CE45015A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3111500" y="460375"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0043EC6-3CC4-3A56-5621-D1995F6C3F82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3730625" y="336550"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>92075</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>92075</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97849794-A0A7-DA48-56C2-4570C6DDB852}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3073400" y="431800"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>225425</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>225425</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C28BE661-1C50-A422-D259-384A17700515}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3883025" y="603250"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60B5195C-E6AB-4996-ADED-BA0AD26B747F}" name="Table1" displayName="Table1" ref="A1:E241" totalsRowShown="0">
-  <autoFilter ref="A1:E241" xr:uid="{60B5195C-E6AB-4996-ADED-BA0AD26B747F}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60B5195C-E6AB-4996-ADED-BA0AD26B747F}" name="Table1" displayName="Table1" ref="A1:F241" totalsRowShown="0">
+  <autoFilter ref="A1:F241" xr:uid="{60B5195C-E6AB-4996-ADED-BA0AD26B747F}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{40C3EB10-60BD-44D1-8F53-D7EE791796A7}" name="country"/>
     <tableColumn id="2" xr3:uid="{8CC024F5-12EA-4F04-AC18-32FA576002EF}" name="organisation"/>
-    <tableColumn id="3" xr3:uid="{6DA6F75D-BB60-43CD-96DE-3E1051CE5B30}" name="month_start" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{6DA6F75D-BB60-43CD-96DE-3E1051CE5B30}" name="month_start" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{D42FF483-FB34-48AB-8A10-F2971B4B8DC6}" name="numerators"/>
     <tableColumn id="5" xr3:uid="{31DFE7BE-2BCE-4D75-B7D7-D171A5593AFA}" name="denominators"/>
+    <tableColumn id="6" xr3:uid="{3BAD4E4F-6219-433A-9B56-9C926EB84164}" name="SD" dataDxfId="12">
+      <calculatedColumnFormula>_xlfn.STDEV.P(Table1[numerators])</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{A813346E-404D-4F12-8ADF-2C9C5833F157}" name="Table12" displayName="Table12" ref="A1:D37" totalsRowShown="0">
+  <autoFilter ref="A1:D37" xr:uid="{A813346E-404D-4F12-8ADF-2C9C5833F157}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{FA93D249-495E-4666-9C03-D7D10953E6F6}" name="Month" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{8262E3AC-7428-4B95-9AB1-5AEB0CE06888}" name="Mean"/>
+    <tableColumn id="3" xr3:uid="{B45622EB-1CD4-4EFE-AB97-7D2E8C93EF27}" name="N"/>
+    <tableColumn id="4" xr3:uid="{676DF2C7-CE97-46BA-83B0-AFDB7D31B34A}" name="SD"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{85C886A0-84A9-4903-B3CA-F0EDC9DFF1DA}" name="Table13" displayName="Table13" ref="A1:C37" totalsRowShown="0">
+  <autoFilter ref="A1:C37" xr:uid="{85C886A0-84A9-4903-B3CA-F0EDC9DFF1DA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C37">
+    <sortCondition ref="A1:A37"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{572A0BDC-CB30-411B-8435-DA91932510B1}" name="Month" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{EE1F8F9A-F408-44AC-925F-00BDF4AE92D7}" name="SD"/>
+    <tableColumn id="3" xr3:uid="{FF45A496-CAC4-4F91-B97B-6E4CD0DF7914}" name="N"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{AE37DBD0-CC3C-4F85-8EDB-68EAD9C8979B}" name="Table14" displayName="Table14" ref="A1:B68" totalsRowShown="0">
+  <autoFilter ref="A1:B68" xr:uid="{AE37DBD0-CC3C-4F85-8EDB-68EAD9C8979B}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{137CF02C-9108-4382-8CB0-737AA1021E4C}" name="Date of Fatality" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{C790EC11-C6D7-45EF-95F4-0210041243C9}" name="Surgeries"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{7F4B3DDD-D82A-4B5C-AE71-47256185F9AD}" name="Table15" displayName="Table15" ref="A1:B68" totalsRowShown="0">
+  <autoFilter ref="A1:B68" xr:uid="{7F4B3DDD-D82A-4B5C-AE71-47256185F9AD}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{948F2CC0-9783-4C85-95B7-2543B353F86A}" name="Date of Fatality" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{2ACA3366-6699-4992-B044-71C5802DB16B}" name="Days"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0597FC6A-6243-4075-BF4F-A5F3DADF53C9}" name="Table_name_test5" displayName="Table_name_test5" ref="A1:B18" totalsRowShown="0">
+  <autoFilter ref="A1:B18" xr:uid="{0597FC6A-6243-4075-BF4F-A5F3DADF53C9}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{DB1E9005-DD79-4D4C-88BC-A9880CDD53AF}" name="Month" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{C960CA6D-8CFF-48C3-9D74-9D1713E0179A}" name="Events"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83B77A84-D877-489A-AC21-D04CD829CB9F}" name="Table_name_test" displayName="Table_name_test" ref="A1:B18" totalsRowShown="0">
+  <autoFilter ref="A1:B18" xr:uid="{83B77A84-D877-489A-AC21-D04CD829CB9F}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{53E01FA9-6511-42AB-93B9-1A7BE3AFF00D}" name="Month" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{0F34ED01-8055-4C38-938D-03F234DD5796}" name="Events"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{695965BD-6171-4E2F-BA1C-3BB8883B27A9}" name="Table6" displayName="Table6" ref="A1:C18" totalsRowShown="0">
+  <autoFilter ref="A1:C18" xr:uid="{695965BD-6171-4E2F-BA1C-3BB8883B27A9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C18">
+    <sortCondition ref="A1:A18"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{4A712F32-8ECE-4FAB-84FE-6D275F8D1630}" name="Month" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{9A49965A-41A2-4364-8DB1-CAE8F75752E9}" name="Events"/>
+    <tableColumn id="3" xr3:uid="{E83D6FC6-367E-40BE-B41E-4F3BA4F2E7EC}" name="Days"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E2B1412F-41F0-47E8-9B0E-8E9D0B624679}" name="Table5" displayName="Table5" ref="A1:C18" totalsRowShown="0">
+  <autoFilter ref="A1:C18" xr:uid="{E2B1412F-41F0-47E8-9B0E-8E9D0B624679}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A5EEE1C8-54ED-4A81-AE44-B611E0A76682}" name="Month" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{06FCF3B1-6BEB-4880-88E6-1CD5E8B7A345}" name="Harmed"/>
+    <tableColumn id="3" xr3:uid="{C77DF6A1-1AAE-480F-A997-913BB55D23A6}" name="Patients"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2103EE76-FA52-45F9-9983-5784574FA0A7}" name="Table8" displayName="Table8" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21" xr:uid="{2103EE76-FA52-45F9-9983-5784574FA0A7}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{32FEBE84-A2FC-4204-8D9C-EEE7DEFBA7CD}" name="Month" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{B0385CE1-D9E6-4740-AA7D-A9B7B2F4654B}" name="Sum of Met Target"/>
+    <tableColumn id="3" xr3:uid="{570AD0E7-363A-4D55-8889-97F6D518DB7E}" name="Sum of Attendances"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BEB0335F-3C9B-4735-BD48-F03A1CC45C50}" name="Table9" displayName="Table9" ref="A1:C18" totalsRowShown="0">
+  <autoFilter ref="A1:C18" xr:uid="{BEB0335F-3C9B-4735-BD48-F03A1CC45C50}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{65B30527-5082-4CCE-850C-1476607224A0}" name="Month" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{D87F9448-8D31-409E-86EB-CBA140E7A39C}" name="Adverse Events"/>
+    <tableColumn id="3" xr3:uid="{68A462E4-A7BC-4292-B7FA-2C6277652A7C}" name="Patient Days"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{861EDEFC-A95E-4AE7-955D-96CE8E9BE7F6}" name="Table10" displayName="Table10" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21" xr:uid="{861EDEFC-A95E-4AE7-955D-96CE8E9BE7F6}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{654FE8AB-0991-4CCF-97FE-8FC9648882A1}" name="Month" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{36A39D84-610F-492D-B472-601D1BBB8818}" name="Sum of Met Target"/>
+    <tableColumn id="3" xr3:uid="{A20A3B92-923D-41A2-9139-67542B22821A}" name="Sum of Attendances"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{941E6763-1C9C-4600-A878-69CD556B5FF3}" name="Table11" displayName="Table11" ref="A1:B37" totalsRowShown="0">
+  <autoFilter ref="A1:B37" xr:uid="{941E6763-1C9C-4600-A878-69CD556B5FF3}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{D47D1A9F-311E-4A81-AF17-452D52C9B04D}" name="Month" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{49BEF797-0FBC-41EC-A401-8027F3CD0411}" name="Events"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -951,18 +1870,38 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="1158" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C4E9B393-DD3D-496C-BFF5-CCEFD87D0BC8}">
+  <we:reference id="cecdfe97-b685-40ad-9d70-3be83089b4e4" version="1.0.0.0" store="developer" storeType="Registry"/>
+  <we:alternateReferences/>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25ED2B5A-2820-4F37-AF8A-902FA9F3F3DC}">
-  <dimension ref="A1:E241"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F241"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.1328125" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -978,8 +1917,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -995,8 +1937,12 @@
       <c r="E2">
         <v>97</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F2">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1012,8 +1958,12 @@
       <c r="E3">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F3">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1029,8 +1979,12 @@
       <c r="E4">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F4">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1046,8 +2000,12 @@
       <c r="E5">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F5">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1063,8 +2021,12 @@
       <c r="E6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F6">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1080,8 +2042,12 @@
       <c r="E7">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F7">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1097,8 +2063,12 @@
       <c r="E8">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F8">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1114,8 +2084,12 @@
       <c r="E9">
         <v>94</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F9">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1131,8 +2105,12 @@
       <c r="E10">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F10">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1148,8 +2126,12 @@
       <c r="E11">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F11">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1165,8 +2147,12 @@
       <c r="E12">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F12">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1182,8 +2168,12 @@
       <c r="E13">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F13">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1199,8 +2189,12 @@
       <c r="E14">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F14">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1216,8 +2210,12 @@
       <c r="E15">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F15">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1233,8 +2231,12 @@
       <c r="E16">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F16">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1250,8 +2252,12 @@
       <c r="E17">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F17">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1267,8 +2273,12 @@
       <c r="E18">
         <v>85</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F18">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1284,8 +2294,12 @@
       <c r="E19">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F19">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1301,8 +2315,12 @@
       <c r="E20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F20">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1318,8 +2336,12 @@
       <c r="E21">
         <v>54</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F21">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1335,8 +2357,12 @@
       <c r="E22">
         <v>89</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F22">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -1352,8 +2378,12 @@
       <c r="E23">
         <v>81</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F23">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1369,8 +2399,12 @@
       <c r="E24">
         <v>84</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F24">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1386,8 +2420,12 @@
       <c r="E25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F25">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1403,8 +2441,12 @@
       <c r="E26">
         <v>39</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F26">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1420,8 +2462,12 @@
       <c r="E27">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F27">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1437,8 +2483,12 @@
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F28">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1454,8 +2504,12 @@
       <c r="E29">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F29">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1471,8 +2525,12 @@
       <c r="E30">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F30">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1488,8 +2546,12 @@
       <c r="E31">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F31">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1505,8 +2567,12 @@
       <c r="E32">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F32">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1522,8 +2588,12 @@
       <c r="E33">
         <v>28</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F33">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1539,8 +2609,12 @@
       <c r="E34">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F34">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1556,8 +2630,12 @@
       <c r="E35">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F35">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1573,8 +2651,12 @@
       <c r="E36">
         <v>54</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F36">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1590,8 +2672,12 @@
       <c r="E37">
         <v>62</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F37">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1607,8 +2693,12 @@
       <c r="E38">
         <v>50</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F38">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1624,8 +2714,12 @@
       <c r="E39">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F39">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1641,8 +2735,12 @@
       <c r="E40">
         <v>46</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F40">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1658,8 +2756,12 @@
       <c r="E41">
         <v>72</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F41">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -1675,8 +2777,12 @@
       <c r="E42">
         <v>82</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F42">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1692,8 +2798,12 @@
       <c r="E43">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F43">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1709,8 +2819,12 @@
       <c r="E44">
         <v>37</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F44">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1726,8 +2840,12 @@
       <c r="E45">
         <v>78</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F45">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1743,8 +2861,12 @@
       <c r="E46">
         <v>36</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F46">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1760,8 +2882,12 @@
       <c r="E47">
         <v>49</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F47">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1777,8 +2903,12 @@
       <c r="E48">
         <v>44</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F48">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1794,8 +2924,12 @@
       <c r="E49">
         <v>76</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F49">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1811,8 +2945,12 @@
       <c r="E50">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F50">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -1828,8 +2966,12 @@
       <c r="E51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F51">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1845,8 +2987,12 @@
       <c r="E52">
         <v>65</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F52">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1862,8 +3008,12 @@
       <c r="E53">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F53">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1879,8 +3029,12 @@
       <c r="E54">
         <v>96</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F54">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -1896,8 +3050,12 @@
       <c r="E55">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F55">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1913,8 +3071,12 @@
       <c r="E56">
         <v>31</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F56">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -1930,8 +3092,12 @@
       <c r="E57">
         <v>89</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F57">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -1947,8 +3113,12 @@
       <c r="E58">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F58">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1964,8 +3134,12 @@
       <c r="E59">
         <v>83</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F59">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -1981,8 +3155,12 @@
       <c r="E60">
         <v>69</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F60">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -1998,8 +3176,12 @@
       <c r="E61">
         <v>32</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F61">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -2015,8 +3197,12 @@
       <c r="E62">
         <v>27</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F62">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -2032,8 +3218,12 @@
       <c r="E63">
         <v>35</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F63">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -2049,8 +3239,12 @@
       <c r="E64">
         <v>84</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F64">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -2066,8 +3260,12 @@
       <c r="E65">
         <v>94</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F65">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -2083,8 +3281,12 @@
       <c r="E66">
         <v>13</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F66">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -2100,8 +3302,12 @@
       <c r="E67">
         <v>74</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F67">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2117,8 +3323,12 @@
       <c r="E68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F68">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2134,8 +3344,12 @@
       <c r="E69">
         <v>85</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F69">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -2151,8 +3365,12 @@
       <c r="E70">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F70">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -2168,8 +3386,12 @@
       <c r="E71">
         <v>44</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F71">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -2185,8 +3407,12 @@
       <c r="E72">
         <v>14</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F72">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -2202,8 +3428,12 @@
       <c r="E73">
         <v>82</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F73">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -2219,8 +3449,12 @@
       <c r="E74">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F74">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>10</v>
       </c>
@@ -2236,8 +3470,12 @@
       <c r="E75">
         <v>53</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F75">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -2253,8 +3491,12 @@
       <c r="E76">
         <v>36</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F76">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -2270,8 +3512,12 @@
       <c r="E77">
         <v>8</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F77">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -2287,8 +3533,12 @@
       <c r="E78">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F78">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -2304,8 +3554,12 @@
       <c r="E79">
         <v>59</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F79">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -2321,8 +3575,12 @@
       <c r="E80">
         <v>97</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F80">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -2338,8 +3596,12 @@
       <c r="E81">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F81">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -2355,8 +3617,12 @@
       <c r="E82">
         <v>63</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F82">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -2372,8 +3638,12 @@
       <c r="E83">
         <v>39</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F83">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -2389,8 +3659,12 @@
       <c r="E84">
         <v>7</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F84">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -2406,8 +3680,12 @@
       <c r="E85">
         <v>71</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F85">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -2423,8 +3701,12 @@
       <c r="E86">
         <v>12</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F86">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -2440,8 +3722,12 @@
       <c r="E87">
         <v>27</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F87">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -2457,8 +3743,12 @@
       <c r="E88">
         <v>72</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F88">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -2474,8 +3764,12 @@
       <c r="E89">
         <v>94</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F89">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -2491,8 +3785,12 @@
       <c r="E90">
         <v>34</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F90">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -2508,8 +3806,12 @@
       <c r="E91">
         <v>35</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F91">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>10</v>
       </c>
@@ -2525,8 +3827,12 @@
       <c r="E92">
         <v>82</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F92">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -2542,8 +3848,12 @@
       <c r="E93">
         <v>95</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F93">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -2559,8 +3869,12 @@
       <c r="E94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F94">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>10</v>
       </c>
@@ -2576,8 +3890,12 @@
       <c r="E95">
         <v>33</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F95">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>10</v>
       </c>
@@ -2593,8 +3911,12 @@
       <c r="E96">
         <v>41</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F96">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -2610,8 +3932,12 @@
       <c r="E97">
         <v>50</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F97">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -2627,8 +3953,12 @@
       <c r="E98">
         <v>3</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F98">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>10</v>
       </c>
@@ -2644,8 +3974,12 @@
       <c r="E99">
         <v>43</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F99">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -2661,8 +3995,12 @@
       <c r="E100">
         <v>74</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F100">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -2678,8 +4016,12 @@
       <c r="E101">
         <v>57</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F101">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -2695,8 +4037,12 @@
       <c r="E102">
         <v>60</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F102">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>10</v>
       </c>
@@ -2712,8 +4058,12 @@
       <c r="E103">
         <v>18</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F103">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -2729,8 +4079,12 @@
       <c r="E104">
         <v>17</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F104">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -2746,8 +4100,12 @@
       <c r="E105">
         <v>78</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F105">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -2763,8 +4121,12 @@
       <c r="E106">
         <v>44</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F106">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -2780,8 +4142,12 @@
       <c r="E107">
         <v>22</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F107">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -2797,8 +4163,12 @@
       <c r="E108">
         <v>95</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F108">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -2814,8 +4184,12 @@
       <c r="E109">
         <v>97</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F109">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -2831,8 +4205,12 @@
       <c r="E110">
         <v>92</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F110">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -2848,8 +4226,12 @@
       <c r="E111">
         <v>71</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F111">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -2865,8 +4247,12 @@
       <c r="E112">
         <v>69</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F112">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -2882,8 +4268,12 @@
       <c r="E113">
         <v>20</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F113">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -2899,8 +4289,12 @@
       <c r="E114">
         <v>73</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F114">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -2916,8 +4310,12 @@
       <c r="E115">
         <v>35</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F115">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -2933,8 +4331,12 @@
       <c r="E116">
         <v>67</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F116">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -2950,8 +4352,12 @@
       <c r="E117">
         <v>96</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F117">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>10</v>
       </c>
@@ -2967,8 +4373,12 @@
       <c r="E118">
         <v>55</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F118">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -2984,8 +4394,12 @@
       <c r="E119">
         <v>33</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F119">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>10</v>
       </c>
@@ -3001,8 +4415,12 @@
       <c r="E120">
         <v>64</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F120">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -3018,8 +4436,12 @@
       <c r="E121">
         <v>52</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F121">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -3035,8 +4457,12 @@
       <c r="E122">
         <v>84</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F122">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -3052,8 +4478,12 @@
       <c r="E123">
         <v>88</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F123">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -3069,8 +4499,12 @@
       <c r="E124">
         <v>52</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F124">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -3086,8 +4520,12 @@
       <c r="E125">
         <v>44</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F125">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3103,8 +4541,12 @@
       <c r="E126">
         <v>32</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F126">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -3120,8 +4562,12 @@
       <c r="E127">
         <v>30</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F127">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -3137,8 +4583,12 @@
       <c r="E128">
         <v>40</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F128">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -3154,8 +4604,12 @@
       <c r="E129">
         <v>55</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F129">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -3171,8 +4625,12 @@
       <c r="E130">
         <v>57</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F130">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -3188,8 +4646,12 @@
       <c r="E131">
         <v>93</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F131">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -3205,8 +4667,12 @@
       <c r="E132">
         <v>67</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F132">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -3222,8 +4688,12 @@
       <c r="E133">
         <v>89</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F133">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -3239,8 +4709,12 @@
       <c r="E134">
         <v>65</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F134">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -3256,8 +4730,12 @@
       <c r="E135">
         <v>3</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F135">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3273,8 +4751,12 @@
       <c r="E136">
         <v>22</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F136">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -3290,8 +4772,12 @@
       <c r="E137">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F137">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -3307,8 +4793,12 @@
       <c r="E138">
         <v>77</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F138">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -3324,8 +4814,12 @@
       <c r="E139">
         <v>87</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F139">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -3341,8 +4835,12 @@
       <c r="E140">
         <v>98</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F140">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -3358,8 +4856,12 @@
       <c r="E141">
         <v>92</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F141">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -3375,8 +4877,12 @@
       <c r="E142">
         <v>97</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F142">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -3392,8 +4898,12 @@
       <c r="E143">
         <v>49</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F143">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -3409,8 +4919,12 @@
       <c r="E144">
         <v>27</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F144">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -3426,8 +4940,12 @@
       <c r="E145">
         <v>43</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F145">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -3443,8 +4961,12 @@
       <c r="E146">
         <v>12</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F146">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -3460,8 +4982,12 @@
       <c r="E147">
         <v>87</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F147">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -3477,8 +5003,12 @@
       <c r="E148">
         <v>24</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F148">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -3494,8 +5024,12 @@
       <c r="E149">
         <v>14</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F149">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -3511,8 +5045,12 @@
       <c r="E150">
         <v>99</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F150">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -3528,8 +5066,12 @@
       <c r="E151">
         <v>62</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F151">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -3545,8 +5087,12 @@
       <c r="E152">
         <v>8</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F152">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -3562,8 +5108,12 @@
       <c r="E153">
         <v>33</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F153">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3579,8 +5129,12 @@
       <c r="E154">
         <v>59</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F154">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -3596,8 +5150,12 @@
       <c r="E155">
         <v>5</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F155">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -3613,8 +5171,12 @@
       <c r="E156">
         <v>4</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F156">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -3630,8 +5192,12 @@
       <c r="E157">
         <v>55</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F157">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -3647,8 +5213,12 @@
       <c r="E158">
         <v>37</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F158">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -3664,8 +5234,12 @@
       <c r="E159">
         <v>20</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F159">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -3681,8 +5255,12 @@
       <c r="E160">
         <v>16</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F160">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -3698,8 +5276,12 @@
       <c r="E161">
         <v>53</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F161">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -3715,8 +5297,12 @@
       <c r="E162">
         <v>90</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F162">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -3732,8 +5318,12 @@
       <c r="E163">
         <v>31</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F163">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>5</v>
       </c>
@@ -3749,8 +5339,12 @@
       <c r="E164">
         <v>78</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F164">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -3766,8 +5360,12 @@
       <c r="E165">
         <v>27</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F165">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -3783,8 +5381,12 @@
       <c r="E166">
         <v>34</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F166">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -3800,8 +5402,12 @@
       <c r="E167">
         <v>66</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F167">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>5</v>
       </c>
@@ -3817,8 +5423,12 @@
       <c r="E168">
         <v>92</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F168">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>5</v>
       </c>
@@ -3834,8 +5444,12 @@
       <c r="E169">
         <v>74</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F169">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -3851,8 +5465,12 @@
       <c r="E170">
         <v>84</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F170">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -3868,8 +5486,12 @@
       <c r="E171">
         <v>47</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F171">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -3885,8 +5507,12 @@
       <c r="E172">
         <v>35</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F172">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -3902,8 +5528,12 @@
       <c r="E173">
         <v>38</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F173">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -3919,8 +5549,12 @@
       <c r="E174">
         <v>20</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F174">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -3936,8 +5570,12 @@
       <c r="E175">
         <v>91</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F175">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -3953,8 +5591,12 @@
       <c r="E176">
         <v>58</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F176">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -3970,8 +5612,12 @@
       <c r="E177">
         <v>55</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F177">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -3987,8 +5633,12 @@
       <c r="E178">
         <v>78</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F178">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -4004,8 +5654,12 @@
       <c r="E179">
         <v>49</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F179">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -4021,8 +5675,12 @@
       <c r="E180">
         <v>4</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F180">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -4038,8 +5696,12 @@
       <c r="E181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F181">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -4055,8 +5717,12 @@
       <c r="E182">
         <v>80</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F182">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>7</v>
       </c>
@@ -4072,8 +5738,12 @@
       <c r="E183">
         <v>56</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F183">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>7</v>
       </c>
@@ -4089,8 +5759,12 @@
       <c r="E184">
         <v>53</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F184">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -4106,8 +5780,12 @@
       <c r="E185">
         <v>10</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F185">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>7</v>
       </c>
@@ -4123,8 +5801,12 @@
       <c r="E186">
         <v>82</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F186">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>7</v>
       </c>
@@ -4140,8 +5822,12 @@
       <c r="E187">
         <v>8</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F187">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>7</v>
       </c>
@@ -4157,8 +5843,12 @@
       <c r="E188">
         <v>61</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F188">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>7</v>
       </c>
@@ -4174,8 +5864,12 @@
       <c r="E189">
         <v>59</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F189">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>7</v>
       </c>
@@ -4191,8 +5885,12 @@
       <c r="E190">
         <v>18</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F190">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>7</v>
       </c>
@@ -4208,8 +5906,12 @@
       <c r="E191">
         <v>88</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F191">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>7</v>
       </c>
@@ -4225,8 +5927,12 @@
       <c r="E192">
         <v>76</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F192">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>7</v>
       </c>
@@ -4242,8 +5948,12 @@
       <c r="E193">
         <v>21</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F193">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -4259,8 +5969,12 @@
       <c r="E194">
         <v>69</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F194">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -4276,8 +5990,12 @@
       <c r="E195">
         <v>16</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F195">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -4293,8 +6011,12 @@
       <c r="E196">
         <v>90</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F196">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -4310,8 +6032,12 @@
       <c r="E197">
         <v>61</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F197">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -4327,8 +6053,12 @@
       <c r="E198">
         <v>13</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F198">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -4344,8 +6074,12 @@
       <c r="E199">
         <v>22</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F199">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -4361,8 +6095,12 @@
       <c r="E200">
         <v>37</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F200">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -4378,8 +6116,12 @@
       <c r="E201">
         <v>66</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F201">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -4395,8 +6137,12 @@
       <c r="E202">
         <v>40</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F202">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -4412,8 +6158,12 @@
       <c r="E203">
         <v>41</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F203">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -4429,8 +6179,12 @@
       <c r="E204">
         <v>28</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F204">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -4446,8 +6200,12 @@
       <c r="E205">
         <v>34</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F205">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -4463,8 +6221,12 @@
       <c r="E206">
         <v>3</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F206">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -4480,8 +6242,12 @@
       <c r="E207">
         <v>84</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F207">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -4497,8 +6263,12 @@
       <c r="E208">
         <v>35</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F208">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -4514,8 +6284,12 @@
       <c r="E209">
         <v>27</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F209">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -4531,8 +6305,12 @@
       <c r="E210">
         <v>97</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F210">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -4548,8 +6326,12 @@
       <c r="E211">
         <v>2</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F211">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -4565,8 +6347,12 @@
       <c r="E212">
         <v>5</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F212">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -4582,8 +6368,12 @@
       <c r="E213">
         <v>36</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F213">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -4599,8 +6389,12 @@
       <c r="E214">
         <v>81</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F214">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -4616,8 +6410,12 @@
       <c r="E215">
         <v>88</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F215">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -4633,8 +6431,12 @@
       <c r="E216">
         <v>19</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F216">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>10</v>
       </c>
@@ -4650,8 +6452,12 @@
       <c r="E217">
         <v>78</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F217">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>5</v>
       </c>
@@ -4667,8 +6473,12 @@
       <c r="E218">
         <v>83</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F218">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -4684,8 +6494,12 @@
       <c r="E219">
         <v>6</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F219">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>5</v>
       </c>
@@ -4701,8 +6515,12 @@
       <c r="E220">
         <v>90</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F220">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -4718,8 +6536,12 @@
       <c r="E221">
         <v>74</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F221">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -4735,8 +6557,12 @@
       <c r="E222">
         <v>87</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F222">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>5</v>
       </c>
@@ -4752,8 +6578,12 @@
       <c r="E223">
         <v>10</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F223">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -4769,8 +6599,12 @@
       <c r="E224">
         <v>52</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F224">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>5</v>
       </c>
@@ -4786,8 +6620,12 @@
       <c r="E225">
         <v>60</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F225">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>5</v>
       </c>
@@ -4803,8 +6641,12 @@
       <c r="E226">
         <v>44</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F226">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -4820,8 +6662,12 @@
       <c r="E227">
         <v>21</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F227">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -4837,8 +6683,12 @@
       <c r="E228">
         <v>70</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F228">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -4854,8 +6704,12 @@
       <c r="E229">
         <v>30</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F229">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -4871,8 +6725,12 @@
       <c r="E230">
         <v>9</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F230">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -4888,8 +6746,12 @@
       <c r="E231">
         <v>66</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F231">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -4905,8 +6767,12 @@
       <c r="E232">
         <v>76</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F232">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>5</v>
       </c>
@@ -4922,8 +6788,12 @@
       <c r="E233">
         <v>95</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F233">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -4939,8 +6809,12 @@
       <c r="E234">
         <v>62</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F234">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -4956,8 +6830,12 @@
       <c r="E235">
         <v>93</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F235">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>5</v>
       </c>
@@ -4973,8 +6851,12 @@
       <c r="E236">
         <v>49</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F236">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -4990,8 +6872,12 @@
       <c r="E237">
         <v>72</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F237">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>5</v>
       </c>
@@ -5007,8 +6893,12 @@
       <c r="E238">
         <v>89</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F238">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -5024,8 +6914,12 @@
       <c r="E239">
         <v>5</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F239">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -5041,8 +6935,12 @@
       <c r="E240">
         <v>28</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F240">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -5057,6 +6955,10 @@
       </c>
       <c r="E241">
         <v>94</v>
+      </c>
+      <c r="F241">
+        <f>_xlfn.STDEV.P(Table1[numerators])</f>
+        <v>9.4894641869578482</v>
       </c>
     </row>
   </sheetData>
@@ -5065,4 +6967,3872 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3B220C-3A50-4B54-B01D-C649E0FAC685}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40725</v>
+      </c>
+      <c r="B2">
+        <v>66.880769230769204</v>
+      </c>
+      <c r="C2">
+        <v>52</v>
+      </c>
+      <c r="D2">
+        <v>8.6085909027762</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40756</v>
+      </c>
+      <c r="B3">
+        <v>68.761484374999995</v>
+      </c>
+      <c r="C3">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>8.7906289699461198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40787</v>
+      </c>
+      <c r="B4">
+        <v>67.7525571428571</v>
+      </c>
+      <c r="C4">
+        <v>70</v>
+      </c>
+      <c r="D4">
+        <v>10.0857497060183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40817</v>
+      </c>
+      <c r="B5">
+        <v>67.046183333333303</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>10.3606397123789</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40848</v>
+      </c>
+      <c r="B6">
+        <v>67.199089552238803</v>
+      </c>
+      <c r="C6">
+        <v>67</v>
+      </c>
+      <c r="D6">
+        <v>10.0489721368359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40878</v>
+      </c>
+      <c r="B7">
+        <v>67.434463768115904</v>
+      </c>
+      <c r="C7">
+        <v>69</v>
+      </c>
+      <c r="D7">
+        <v>8.8747874889107194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40909</v>
+      </c>
+      <c r="B8">
+        <v>69.227089552238795</v>
+      </c>
+      <c r="C8">
+        <v>67</v>
+      </c>
+      <c r="D8">
+        <v>9.4357162866803606</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40940</v>
+      </c>
+      <c r="B9">
+        <v>71.117574074074</v>
+      </c>
+      <c r="C9">
+        <v>54</v>
+      </c>
+      <c r="D9">
+        <v>9.4394819529891691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40969</v>
+      </c>
+      <c r="B10">
+        <v>67.630037974683503</v>
+      </c>
+      <c r="C10">
+        <v>79</v>
+      </c>
+      <c r="D10">
+        <v>11.1521380040711</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>41000</v>
+      </c>
+      <c r="B11">
+        <v>69.9717118644067</v>
+      </c>
+      <c r="C11">
+        <v>59</v>
+      </c>
+      <c r="D11">
+        <v>8.42396803326392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>41030</v>
+      </c>
+      <c r="B12">
+        <v>66.668204081632595</v>
+      </c>
+      <c r="C12">
+        <v>49</v>
+      </c>
+      <c r="D12">
+        <v>8.9510993008145991</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>41061</v>
+      </c>
+      <c r="B13">
+        <v>67.762721311475403</v>
+      </c>
+      <c r="C13">
+        <v>61</v>
+      </c>
+      <c r="D13">
+        <v>10.731890179459301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>41091</v>
+      </c>
+      <c r="B14">
+        <v>69.324926829268193</v>
+      </c>
+      <c r="C14">
+        <v>41</v>
+      </c>
+      <c r="D14">
+        <v>8.6952501061947096</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>41122</v>
+      </c>
+      <c r="B15">
+        <v>66.037999999999997</v>
+      </c>
+      <c r="C15">
+        <v>51</v>
+      </c>
+      <c r="D15">
+        <v>9.5560205906754394</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>41153</v>
+      </c>
+      <c r="B16">
+        <v>67.610071428571402</v>
+      </c>
+      <c r="C16">
+        <v>56</v>
+      </c>
+      <c r="D16">
+        <v>10.3161198440961</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>41183</v>
+      </c>
+      <c r="B17">
+        <v>69.693581395348801</v>
+      </c>
+      <c r="C17">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>9.9618027583798305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>41214</v>
+      </c>
+      <c r="B18">
+        <v>67.620070175438599</v>
+      </c>
+      <c r="C18">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>9.6096906203913193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>41244</v>
+      </c>
+      <c r="B19">
+        <v>67.313124999999999</v>
+      </c>
+      <c r="C19">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>9.2557775439294403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>41275</v>
+      </c>
+      <c r="B20">
+        <v>68.4106376811594</v>
+      </c>
+      <c r="C20">
+        <v>69</v>
+      </c>
+      <c r="D20">
+        <v>8.4394797678994298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>41306</v>
+      </c>
+      <c r="B21">
+        <v>64.726317073170705</v>
+      </c>
+      <c r="C21">
+        <v>41</v>
+      </c>
+      <c r="D21">
+        <v>9.4723407425707897</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>41334</v>
+      </c>
+      <c r="B22">
+        <v>68.278199999999998</v>
+      </c>
+      <c r="C22">
+        <v>40</v>
+      </c>
+      <c r="D22">
+        <v>9.5975243010892406</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>41365</v>
+      </c>
+      <c r="B23">
+        <v>69.340347826086898</v>
+      </c>
+      <c r="C23">
+        <v>46</v>
+      </c>
+      <c r="D23">
+        <v>8.7946563623140097</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>41395</v>
+      </c>
+      <c r="B24">
+        <v>66.529355932203302</v>
+      </c>
+      <c r="C24">
+        <v>59</v>
+      </c>
+      <c r="D24">
+        <v>9.9011828102910293</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>41426</v>
+      </c>
+      <c r="B25">
+        <v>66.665112903225804</v>
+      </c>
+      <c r="C25">
+        <v>62</v>
+      </c>
+      <c r="D25">
+        <v>10.6528050707009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>41456</v>
+      </c>
+      <c r="B26">
+        <v>67.269263157894699</v>
+      </c>
+      <c r="C26">
+        <v>57</v>
+      </c>
+      <c r="D26">
+        <v>9.5917635967353405</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>41487</v>
+      </c>
+      <c r="B27">
+        <v>67.693307692307599</v>
+      </c>
+      <c r="C27">
+        <v>65</v>
+      </c>
+      <c r="D27">
+        <v>9.5528095261963397</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>41518</v>
+      </c>
+      <c r="B28">
+        <v>67.599293333333307</v>
+      </c>
+      <c r="C28">
+        <v>75</v>
+      </c>
+      <c r="D28">
+        <v>9.6754394391480396</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>41548</v>
+      </c>
+      <c r="B29">
+        <v>67.293728571428503</v>
+      </c>
+      <c r="C29">
+        <v>70</v>
+      </c>
+      <c r="D29">
+        <v>10.278452158237799</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>41579</v>
+      </c>
+      <c r="B30">
+        <v>68.465802631578896</v>
+      </c>
+      <c r="C30">
+        <v>76</v>
+      </c>
+      <c r="D30">
+        <v>8.5974976393376394</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>41609</v>
+      </c>
+      <c r="B31">
+        <v>66.824318840579707</v>
+      </c>
+      <c r="C31">
+        <v>69</v>
+      </c>
+      <c r="D31">
+        <v>9.8033121443617208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>41640</v>
+      </c>
+      <c r="B32">
+        <v>68.872343749999999</v>
+      </c>
+      <c r="C32">
+        <v>64</v>
+      </c>
+      <c r="D32">
+        <v>7.8372733344789296</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>41671</v>
+      </c>
+      <c r="B33">
+        <v>66.752373134328295</v>
+      </c>
+      <c r="C33">
+        <v>67</v>
+      </c>
+      <c r="D33">
+        <v>8.8850727910671807</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>41699</v>
+      </c>
+      <c r="B34">
+        <v>67.407273809523801</v>
+      </c>
+      <c r="C34">
+        <v>84</v>
+      </c>
+      <c r="D34">
+        <v>9.3973397911971599</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>41730</v>
+      </c>
+      <c r="B35">
+        <v>69.867208955223802</v>
+      </c>
+      <c r="C35">
+        <v>67</v>
+      </c>
+      <c r="D35">
+        <v>9.7320308299828895</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>41760</v>
+      </c>
+      <c r="B36">
+        <v>68.190144927536195</v>
+      </c>
+      <c r="C36">
+        <v>69</v>
+      </c>
+      <c r="D36">
+        <v>8.5165372688354495</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>41791</v>
+      </c>
+      <c r="B37">
+        <v>66.044525641025601</v>
+      </c>
+      <c r="C37">
+        <v>78</v>
+      </c>
+      <c r="D37">
+        <v>11.113743957918199</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A69703-9BBF-41C0-9DA0-7B57125EA047}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40725</v>
+      </c>
+      <c r="B2">
+        <v>8.6085909027762</v>
+      </c>
+      <c r="C2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40756</v>
+      </c>
+      <c r="B3">
+        <v>8.7906289699461198</v>
+      </c>
+      <c r="C3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40787</v>
+      </c>
+      <c r="B4">
+        <v>10.0857497060183</v>
+      </c>
+      <c r="C4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40817</v>
+      </c>
+      <c r="B5">
+        <v>10.3606397123789</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40848</v>
+      </c>
+      <c r="B6">
+        <v>10.0489721368359</v>
+      </c>
+      <c r="C6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40878</v>
+      </c>
+      <c r="B7">
+        <v>8.8747874889107194</v>
+      </c>
+      <c r="C7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40909</v>
+      </c>
+      <c r="B8">
+        <v>9.4357162866803606</v>
+      </c>
+      <c r="C8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40940</v>
+      </c>
+      <c r="B9">
+        <v>9.4394819529891691</v>
+      </c>
+      <c r="C9">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40969</v>
+      </c>
+      <c r="B10">
+        <v>11.1521380040711</v>
+      </c>
+      <c r="C10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>41000</v>
+      </c>
+      <c r="B11">
+        <v>8.42396803326392</v>
+      </c>
+      <c r="C11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>41030</v>
+      </c>
+      <c r="B12">
+        <v>8.9510993008145991</v>
+      </c>
+      <c r="C12">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>41061</v>
+      </c>
+      <c r="B13">
+        <v>10.731890179459301</v>
+      </c>
+      <c r="C13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>41091</v>
+      </c>
+      <c r="B14">
+        <v>8.6952501061947096</v>
+      </c>
+      <c r="C14">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>41122</v>
+      </c>
+      <c r="B15">
+        <v>9.5560205906754394</v>
+      </c>
+      <c r="C15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>41153</v>
+      </c>
+      <c r="B16">
+        <v>10.3161198440961</v>
+      </c>
+      <c r="C16">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>41183</v>
+      </c>
+      <c r="B17">
+        <v>9.9618027583798305</v>
+      </c>
+      <c r="C17">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>41214</v>
+      </c>
+      <c r="B18">
+        <v>9.6096906203913193</v>
+      </c>
+      <c r="C18">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>41244</v>
+      </c>
+      <c r="B19">
+        <v>9.2557775439294403</v>
+      </c>
+      <c r="C19">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>41275</v>
+      </c>
+      <c r="B20">
+        <v>8.4394797678994298</v>
+      </c>
+      <c r="C20">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>41306</v>
+      </c>
+      <c r="B21">
+        <v>9.4723407425707897</v>
+      </c>
+      <c r="C21">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>41334</v>
+      </c>
+      <c r="B22">
+        <v>9.5975243010892406</v>
+      </c>
+      <c r="C22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>41365</v>
+      </c>
+      <c r="B23">
+        <v>8.7946563623140097</v>
+      </c>
+      <c r="C23">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>41395</v>
+      </c>
+      <c r="B24">
+        <v>9.9011828102910293</v>
+      </c>
+      <c r="C24">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>41426</v>
+      </c>
+      <c r="B25">
+        <v>10.6528050707009</v>
+      </c>
+      <c r="C25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>41456</v>
+      </c>
+      <c r="B26">
+        <v>9.5917635967353405</v>
+      </c>
+      <c r="C26">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>41487</v>
+      </c>
+      <c r="B27">
+        <v>9.5528095261963397</v>
+      </c>
+      <c r="C27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>41518</v>
+      </c>
+      <c r="B28">
+        <v>9.6754394391480396</v>
+      </c>
+      <c r="C28">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>41548</v>
+      </c>
+      <c r="B29">
+        <v>10.278452158237799</v>
+      </c>
+      <c r="C29">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>41579</v>
+      </c>
+      <c r="B30">
+        <v>8.5974976393376394</v>
+      </c>
+      <c r="C30">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>41609</v>
+      </c>
+      <c r="B31">
+        <v>9.8033121443617208</v>
+      </c>
+      <c r="C31">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>41640</v>
+      </c>
+      <c r="B32">
+        <v>7.8372733344789296</v>
+      </c>
+      <c r="C32">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>41671</v>
+      </c>
+      <c r="B33">
+        <v>8.8850727910671807</v>
+      </c>
+      <c r="C33">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>41699</v>
+      </c>
+      <c r="B34">
+        <v>9.3973397911971599</v>
+      </c>
+      <c r="C34">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>41730</v>
+      </c>
+      <c r="B35">
+        <v>9.7320308299828895</v>
+      </c>
+      <c r="C35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>41760</v>
+      </c>
+      <c r="B36">
+        <v>8.5165372688354495</v>
+      </c>
+      <c r="C36">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>41791</v>
+      </c>
+      <c r="B37">
+        <v>11.113743957918199</v>
+      </c>
+      <c r="C37">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1914B0D5-C1FB-4999-BF2C-D6B56FAF3D9A}">
+  <dimension ref="A1:B68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40761</v>
+      </c>
+      <c r="B2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40781</v>
+      </c>
+      <c r="B3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40786</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40799</v>
+      </c>
+      <c r="B5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40800</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40826</v>
+      </c>
+      <c r="B7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40872</v>
+      </c>
+      <c r="B8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40884</v>
+      </c>
+      <c r="B9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40896</v>
+      </c>
+      <c r="B10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40901</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40920</v>
+      </c>
+      <c r="B12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40924</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40927</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40942</v>
+      </c>
+      <c r="B15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40956</v>
+      </c>
+      <c r="B16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40965</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40973</v>
+      </c>
+      <c r="B18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>40988</v>
+      </c>
+      <c r="B19">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>41009</v>
+      </c>
+      <c r="B20">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>41015</v>
+      </c>
+      <c r="B21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>41018</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>41019</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>41075</v>
+      </c>
+      <c r="B24">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>41192</v>
+      </c>
+      <c r="B25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>41193</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>41226</v>
+      </c>
+      <c r="B27">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>41235</v>
+      </c>
+      <c r="B28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>41244</v>
+      </c>
+      <c r="B29">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>41263</v>
+      </c>
+      <c r="B30">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>41275</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>41276</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>41292</v>
+      </c>
+      <c r="B33">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>41305</v>
+      </c>
+      <c r="B34">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>41323</v>
+      </c>
+      <c r="B35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>41324</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>41359</v>
+      </c>
+      <c r="B37">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>41375</v>
+      </c>
+      <c r="B38">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>41380</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>41401</v>
+      </c>
+      <c r="B40">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>41439</v>
+      </c>
+      <c r="B41">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41442</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>41467</v>
+      </c>
+      <c r="B43">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>41470</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>41481</v>
+      </c>
+      <c r="B45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>41494</v>
+      </c>
+      <c r="B46">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>41514</v>
+      </c>
+      <c r="B47">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>41523</v>
+      </c>
+      <c r="B48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>41526</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>41534</v>
+      </c>
+      <c r="B50">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>41555</v>
+      </c>
+      <c r="B51">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>41579</v>
+      </c>
+      <c r="B52">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>41617</v>
+      </c>
+      <c r="B53">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>41625</v>
+      </c>
+      <c r="B54">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>41638</v>
+      </c>
+      <c r="B55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>41647</v>
+      </c>
+      <c r="B56">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>41648</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>41678</v>
+      </c>
+      <c r="B58">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>41701</v>
+      </c>
+      <c r="B59">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>41704</v>
+      </c>
+      <c r="B60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>41711</v>
+      </c>
+      <c r="B61">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>41733</v>
+      </c>
+      <c r="B62">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>41752</v>
+      </c>
+      <c r="B63">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>41763</v>
+      </c>
+      <c r="B64">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>41794</v>
+      </c>
+      <c r="B65">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>41800</v>
+      </c>
+      <c r="B66">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>41801</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>41802</v>
+      </c>
+      <c r="B68">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94239D50-9E27-4C78-8D79-9458660D580C}">
+  <dimension ref="A1:B68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40761</v>
+      </c>
+      <c r="B2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40781</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40786</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40799</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40800</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40826</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40872</v>
+      </c>
+      <c r="B8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40884</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40896</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40901</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40920</v>
+      </c>
+      <c r="B12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40924</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40927</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40942</v>
+      </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40956</v>
+      </c>
+      <c r="B16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40965</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40973</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>40988</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>41009</v>
+      </c>
+      <c r="B20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>41015</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>41018</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>41019</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>41075</v>
+      </c>
+      <c r="B24">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>41192</v>
+      </c>
+      <c r="B25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>41193</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>41226</v>
+      </c>
+      <c r="B27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>41235</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>41244</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>41263</v>
+      </c>
+      <c r="B30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>41275</v>
+      </c>
+      <c r="B31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>41276</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>41292</v>
+      </c>
+      <c r="B33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>41305</v>
+      </c>
+      <c r="B34">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>41323</v>
+      </c>
+      <c r="B35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>41324</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>41359</v>
+      </c>
+      <c r="B37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>41375</v>
+      </c>
+      <c r="B38">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>41380</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>41401</v>
+      </c>
+      <c r="B40">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>41439</v>
+      </c>
+      <c r="B41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41442</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>41467</v>
+      </c>
+      <c r="B43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>41470</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>41481</v>
+      </c>
+      <c r="B45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>41494</v>
+      </c>
+      <c r="B46">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>41514</v>
+      </c>
+      <c r="B47">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>41523</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>41526</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>41534</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>41555</v>
+      </c>
+      <c r="B51">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>41579</v>
+      </c>
+      <c r="B52">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>41617</v>
+      </c>
+      <c r="B53">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>41625</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>41638</v>
+      </c>
+      <c r="B55">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>41647</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>41648</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>41678</v>
+      </c>
+      <c r="B58">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>41701</v>
+      </c>
+      <c r="B59">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>41704</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>41711</v>
+      </c>
+      <c r="B61">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>41733</v>
+      </c>
+      <c r="B62">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>41752</v>
+      </c>
+      <c r="B63">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>41763</v>
+      </c>
+      <c r="B64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>41794</v>
+      </c>
+      <c r="B65">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>41800</v>
+      </c>
+      <c r="B66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>41801</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>41802</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91ED3F9-FD8B-42B8-9B02-B889A07F00F1}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40179</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40210</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40238</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40269</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40299</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40330</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40360</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40391</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40422</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40452</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40483</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40513</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40544</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40575</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40603</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40634</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40664</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5F4E47-B510-4624-9D60-F67EBAAAEFFA}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40179</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40210</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40238</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40269</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40299</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40330</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40360</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40391</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40422</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40452</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40483</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40513</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40544</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40575</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40603</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40634</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40664</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A1EBBE-BFA0-4C2A-8F00-D92C78290E2D}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40179</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40210</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40238</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40269</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40299</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40330</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40360</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40391</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40422</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40452</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40483</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40513</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40544</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40575</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40603</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40634</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40664</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC891C-EE34-4005-8E2B-CDF24F154389}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40179</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40210</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40238</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40269</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40299</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40330</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40360</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40391</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40422</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40452</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40483</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40513</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40544</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40575</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40603</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40634</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40664</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40DFCC3A-ECD0-4F8D-A9CF-8CB6D6A9105E}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>36526</v>
+      </c>
+      <c r="B2">
+        <v>266501</v>
+      </c>
+      <c r="C2">
+        <v>280443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>36557</v>
+      </c>
+      <c r="B3">
+        <v>264225</v>
+      </c>
+      <c r="C3">
+        <v>276823</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>36586</v>
+      </c>
+      <c r="B4">
+        <v>276532</v>
+      </c>
+      <c r="C4">
+        <v>291681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>36617</v>
+      </c>
+      <c r="B5">
+        <v>281461</v>
+      </c>
+      <c r="C5">
+        <v>296155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>36647</v>
+      </c>
+      <c r="B6">
+        <v>269071</v>
+      </c>
+      <c r="C6">
+        <v>282343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>36678</v>
+      </c>
+      <c r="B7">
+        <v>261215</v>
+      </c>
+      <c r="C7">
+        <v>275888</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>36708</v>
+      </c>
+      <c r="B8">
+        <v>270409</v>
+      </c>
+      <c r="C8">
+        <v>283867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>36739</v>
+      </c>
+      <c r="B9">
+        <v>279778</v>
+      </c>
+      <c r="C9">
+        <v>295251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>36770</v>
+      </c>
+      <c r="B10">
+        <v>270483</v>
+      </c>
+      <c r="C10">
+        <v>284468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>36800</v>
+      </c>
+      <c r="B11">
+        <v>270320</v>
+      </c>
+      <c r="C11">
+        <v>282529</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>36831</v>
+      </c>
+      <c r="B12">
+        <v>267923</v>
+      </c>
+      <c r="C12">
+        <v>279618</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>36861</v>
+      </c>
+      <c r="B13">
+        <v>271478</v>
+      </c>
+      <c r="C13">
+        <v>283932</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>36892</v>
+      </c>
+      <c r="B14">
+        <v>255353</v>
+      </c>
+      <c r="C14">
+        <v>266629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>36923</v>
+      </c>
+      <c r="B15">
+        <v>256820</v>
+      </c>
+      <c r="C15">
+        <v>268091</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>36951</v>
+      </c>
+      <c r="B16">
+        <v>261835</v>
+      </c>
+      <c r="C16">
+        <v>276803</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>36982</v>
+      </c>
+      <c r="B17">
+        <v>259144</v>
+      </c>
+      <c r="C17">
+        <v>271578</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>37012</v>
+      </c>
+      <c r="B18">
+        <v>255910</v>
+      </c>
+      <c r="C18">
+        <v>266005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>37043</v>
+      </c>
+      <c r="B19">
+        <v>260863</v>
+      </c>
+      <c r="C19">
+        <v>273520</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>37073</v>
+      </c>
+      <c r="B20">
+        <v>264465</v>
+      </c>
+      <c r="C20">
+        <v>278574</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>37104</v>
+      </c>
+      <c r="B21">
+        <v>260989</v>
+      </c>
+      <c r="C21">
+        <v>273772</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAC2F81D-A205-4DCE-B517-1B59A705DB10}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>40179</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>40210</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>40238</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>40269</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>40299</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>40330</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>40360</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>40391</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>40422</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>40452</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>40483</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>40513</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>40544</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>40575</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>40603</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>40634</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>40664</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B3C8B1-CD5A-4815-86FC-BCE94FBA487A}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>36526</v>
+      </c>
+      <c r="B2">
+        <v>266501</v>
+      </c>
+      <c r="C2">
+        <v>280443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>36557</v>
+      </c>
+      <c r="B3">
+        <v>264225</v>
+      </c>
+      <c r="C3">
+        <v>276823</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>36586</v>
+      </c>
+      <c r="B4">
+        <v>276532</v>
+      </c>
+      <c r="C4">
+        <v>291681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>36617</v>
+      </c>
+      <c r="B5">
+        <v>281461</v>
+      </c>
+      <c r="C5">
+        <v>296155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>36647</v>
+      </c>
+      <c r="B6">
+        <v>269071</v>
+      </c>
+      <c r="C6">
+        <v>282343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>36678</v>
+      </c>
+      <c r="B7">
+        <v>261215</v>
+      </c>
+      <c r="C7">
+        <v>275888</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>36708</v>
+      </c>
+      <c r="B8">
+        <v>270409</v>
+      </c>
+      <c r="C8">
+        <v>283867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>36739</v>
+      </c>
+      <c r="B9">
+        <v>279778</v>
+      </c>
+      <c r="C9">
+        <v>295251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>36770</v>
+      </c>
+      <c r="B10">
+        <v>270483</v>
+      </c>
+      <c r="C10">
+        <v>284468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>36800</v>
+      </c>
+      <c r="B11">
+        <v>270320</v>
+      </c>
+      <c r="C11">
+        <v>282529</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>36831</v>
+      </c>
+      <c r="B12">
+        <v>267923</v>
+      </c>
+      <c r="C12">
+        <v>279618</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>36861</v>
+      </c>
+      <c r="B13">
+        <v>271478</v>
+      </c>
+      <c r="C13">
+        <v>283932</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>36892</v>
+      </c>
+      <c r="B14">
+        <v>255353</v>
+      </c>
+      <c r="C14">
+        <v>266629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>36923</v>
+      </c>
+      <c r="B15">
+        <v>256820</v>
+      </c>
+      <c r="C15">
+        <v>268091</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>36951</v>
+      </c>
+      <c r="B16">
+        <v>261835</v>
+      </c>
+      <c r="C16">
+        <v>276803</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>36982</v>
+      </c>
+      <c r="B17">
+        <v>259144</v>
+      </c>
+      <c r="C17">
+        <v>271578</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>37012</v>
+      </c>
+      <c r="B18">
+        <v>255910</v>
+      </c>
+      <c r="C18">
+        <v>266005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>37043</v>
+      </c>
+      <c r="B19">
+        <v>260863</v>
+      </c>
+      <c r="C19">
+        <v>273520</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>37073</v>
+      </c>
+      <c r="B20">
+        <v>264465</v>
+      </c>
+      <c r="C20">
+        <v>278574</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>37104</v>
+      </c>
+      <c r="B21">
+        <v>260989</v>
+      </c>
+      <c r="C21">
+        <v>273772</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C606FF9A-90E0-4BFC-996A-18738DF4D853}">
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>41214</v>
+      </c>
+      <c r="B2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>41244</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>41275</v>
+      </c>
+      <c r="B4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>41306</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>41334</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>41365</v>
+      </c>
+      <c r="B7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>41395</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>41426</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>41456</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>41487</v>
+      </c>
+      <c r="B11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>41518</v>
+      </c>
+      <c r="B12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>41548</v>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>41579</v>
+      </c>
+      <c r="B14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>41609</v>
+      </c>
+      <c r="B15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>41640</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>41671</v>
+      </c>
+      <c r="B17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>41699</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>41730</v>
+      </c>
+      <c r="B19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>41760</v>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>41791</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>41821</v>
+      </c>
+      <c r="B22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>41852</v>
+      </c>
+      <c r="B23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>41883</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>41913</v>
+      </c>
+      <c r="B25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>41944</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>41974</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>42005</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>42036</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>42064</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>42095</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>42125</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>42156</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>42186</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>42217</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>42248</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>42278</v>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/assets/dummy_data.xlsx
+++ b/assets/dummy_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\he162696\Documents\ExcelControlCharts\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\he162696\REPOS\ExcelControlCharts\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B90C4CA-ECCD-4D42-9CCF-FEEEA7954A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1386BD34-3ECC-4697-83F5-EA77D6120D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="20640" windowHeight="13200" tabRatio="752" firstSheet="1" activeTab="1" xr2:uid="{B4DE27E6-3CDA-4D86-9B4B-E26F47FA9977}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="752" activeTab="1" xr2:uid="{B4DE27E6-3CDA-4D86-9B4B-E26F47FA9977}"/>
   </bookViews>
   <sheets>
     <sheet name="dummy_data" sheetId="1" r:id="rId1"/>
@@ -957,22 +957,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>187325</xdr:colOff>
+      <xdr:colOff>325437</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>153193</xdr:rowOff>
+      <xdr:rowOff>12699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>79374</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>325437</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>12699</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image">
+        <xdr:cNvPr id="2" name="Image">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F734B5-59F4-5617-E721-9B86624FB317}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8595ADDF-F199-DA02-6B55-BDD86B2120F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -994,8 +994,208 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2835275" y="1105693"/>
-          <a:ext cx="5489575" cy="4117181"/>
+          <a:off x="2973387" y="965199"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F3CF22D-7110-FFFE-1E2F-B42640A7DF9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2825750" y="984250"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>155575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>155575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C87C8559-08B0-D9E4-A2B5-D4CFDCEC3C3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3073400" y="1298575"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2AD3AC7-F76E-E14C-E879-ADCA9803B5B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2463800" y="889000"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1254125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>117475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>434975</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>117475</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5EB59A2-2BBE-50AB-D552-0EDFE8020326}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1254125" y="688975"/>
+          <a:ext cx="6096000" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1066,16 +1266,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>434975</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>434975</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1104,7 +1304,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3787775" y="946150"/>
+          <a:off x="3149600" y="746125"/>
           <a:ext cx="6096000" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1121,16 +1321,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>530225</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>98425</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>554038</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>179388</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>530225</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>98425</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>554038</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>179388</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1159,7 +1359,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3835400" y="479425"/>
+          <a:off x="4468813" y="941388"/>
           <a:ext cx="6096000" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1463,7 +1663,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0597FC6A-6243-4075-BF4F-A5F3DADF53C9}" name="Table_name_test5" displayName="Table_name_test5" ref="A1:B18" totalsRowShown="0">
   <autoFilter ref="A1:B18" xr:uid="{0597FC6A-6243-4075-BF4F-A5F3DADF53C9}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DB1E9005-DD79-4D4C-88BC-A9880CDD53AF}" name="Month" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{DB1E9005-DD79-4D4C-88BC-A9880CDD53AF}" name="Month" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{C960CA6D-8CFF-48C3-9D74-9D1713E0179A}" name="Events"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1474,7 +1674,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83B77A84-D877-489A-AC21-D04CD829CB9F}" name="Table_name_test" displayName="Table_name_test" ref="A1:B18" totalsRowShown="0">
   <autoFilter ref="A1:B18" xr:uid="{83B77A84-D877-489A-AC21-D04CD829CB9F}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{53E01FA9-6511-42AB-93B9-1A7BE3AFF00D}" name="Month" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{53E01FA9-6511-42AB-93B9-1A7BE3AFF00D}" name="Month" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{0F34ED01-8055-4C38-938D-03F234DD5796}" name="Events"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1488,7 +1688,7 @@
     <sortCondition ref="A1:A18"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{4A712F32-8ECE-4FAB-84FE-6D275F8D1630}" name="Month" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{4A712F32-8ECE-4FAB-84FE-6D275F8D1630}" name="Month" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{9A49965A-41A2-4364-8DB1-CAE8F75752E9}" name="Events"/>
     <tableColumn id="3" xr3:uid="{E83D6FC6-367E-40BE-B41E-4F3BA4F2E7EC}" name="Days"/>
   </tableColumns>
@@ -1500,7 +1700,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E2B1412F-41F0-47E8-9B0E-8E9D0B624679}" name="Table5" displayName="Table5" ref="A1:C18" totalsRowShown="0">
   <autoFilter ref="A1:C18" xr:uid="{E2B1412F-41F0-47E8-9B0E-8E9D0B624679}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A5EEE1C8-54ED-4A81-AE44-B611E0A76682}" name="Month" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{A5EEE1C8-54ED-4A81-AE44-B611E0A76682}" name="Month" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{06FCF3B1-6BEB-4880-88E6-1CD5E8B7A345}" name="Harmed"/>
     <tableColumn id="3" xr3:uid="{C77DF6A1-1AAE-480F-A997-913BB55D23A6}" name="Patients"/>
   </tableColumns>
@@ -1872,7 +2072,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="1158" row="5">
+  <wetp:taskpane dockstate="right" visibility="0" width="606" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -9303,7 +9503,7 @@
         <v>40452</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -9335,7 +9535,7 @@
         <v>40575</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -9343,7 +9543,7 @@
         <v>40603</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -9351,7 +9551,7 @@
         <v>40634</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -9359,7 +9559,7 @@
         <v>40664</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">

--- a/assets/dummy_data.xlsx
+++ b/assets/dummy_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\he162696\REPOS\ExcelControlCharts\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1386BD34-3ECC-4697-83F5-EA77D6120D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B21B4-19B8-4693-AB92-41E0338F09F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="752" activeTab="1" xr2:uid="{B4DE27E6-3CDA-4D86-9B4B-E26F47FA9977}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="752" firstSheet="1" activeTab="12" xr2:uid="{B4DE27E6-3CDA-4D86-9B4B-E26F47FA9977}"/>
   </bookViews>
   <sheets>
     <sheet name="dummy_data" sheetId="1" r:id="rId1"/>
@@ -846,16 +846,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>587375</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>357187</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>93662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>587375</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>357187</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>93662</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -884,8 +884,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3092450" y="412750"/>
-          <a:ext cx="6096000" cy="4572000"/>
+          <a:off x="4087812" y="474662"/>
+          <a:ext cx="6111875" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -902,15 +902,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>530225</xdr:colOff>
+      <xdr:colOff>511175</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>174625</xdr:rowOff>
+      <xdr:rowOff>168275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>530225</xdr:colOff>
+      <xdr:colOff>511175</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>174625</xdr:rowOff>
+      <xdr:rowOff>168275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -939,7 +939,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2863850" y="555625"/>
+          <a:off x="3654425" y="549275"/>
           <a:ext cx="6096000" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -956,23 +956,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>325437</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>134939</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>325437</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>134939</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image">
+        <xdr:cNvPr id="6" name="Image">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8595ADDF-F199-DA02-6B55-BDD86B2120F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5EB59A2-2BBE-50AB-D552-0EDFE8020326}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -994,208 +994,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2973387" y="965199"/>
-          <a:ext cx="6096000" cy="4572000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F3CF22D-7110-FFFE-1E2F-B42640A7DF9B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2825750" y="984250"/>
-          <a:ext cx="6096000" cy="4572000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>155575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>155575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C87C8559-08B0-D9E4-A2B5-D4CFDCEC3C3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3073400" y="1298575"/>
-          <a:ext cx="6096000" cy="4572000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2AD3AC7-F76E-E14C-E879-ADCA9803B5B2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2463800" y="889000"/>
-          <a:ext cx="6096000" cy="4572000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1254125</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>117475</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>434975</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>117475</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5EB59A2-2BBE-50AB-D552-0EDFE8020326}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1254125" y="688975"/>
-          <a:ext cx="6096000" cy="4572000"/>
+          <a:off x="5480050" y="896939"/>
+          <a:ext cx="6191250" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2072,7 +1872,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="606" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="348" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -8692,7 +8492,8 @@
   <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
